--- a/artfynd/A 33954-2024 artfynd.xlsx
+++ b/artfynd/A 33954-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,116 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120249068</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Klövsjön 3, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>613564</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6561341</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33954-2024 artfynd.xlsx
+++ b/artfynd/A 33954-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120217666</v>
       </c>
       <c r="B2" t="n">
-        <v>91883</v>
+        <v>91901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>120249068</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 33954-2024 artfynd.xlsx
+++ b/artfynd/A 33954-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -885,6 +885,112 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122747228</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92118</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svarttj. SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>613616</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6561364</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33954-2024 artfynd.xlsx
+++ b/artfynd/A 33954-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122747228</v>
       </c>
       <c r="B4" t="n">
-        <v>92221</v>
+        <v>92225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 33954-2024 artfynd.xlsx
+++ b/artfynd/A 33954-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122747228</v>
       </c>
       <c r="B4" t="n">
-        <v>92225</v>
+        <v>92233</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 33954-2024 artfynd.xlsx
+++ b/artfynd/A 33954-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122747228</v>
       </c>
       <c r="B4" t="n">
-        <v>92233</v>
+        <v>92236</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 33954-2024 artfynd.xlsx
+++ b/artfynd/A 33954-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122747228</v>
       </c>
       <c r="B4" t="n">
-        <v>92236</v>
+        <v>92238</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 33954-2024 artfynd.xlsx
+++ b/artfynd/A 33954-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122747228</v>
       </c>
       <c r="B4" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33954-2024 artfynd.xlsx
+++ b/artfynd/A 33954-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122747228</v>
       </c>
       <c r="B4" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33954-2024 artfynd.xlsx
+++ b/artfynd/A 33954-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122747228</v>
       </c>
       <c r="B4" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33954-2024 artfynd.xlsx
+++ b/artfynd/A 33954-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122747228</v>
       </c>
       <c r="B4" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33954-2024 artfynd.xlsx
+++ b/artfynd/A 33954-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122747228</v>
       </c>
       <c r="B4" t="n">
-        <v>93197</v>
+        <v>93198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33954-2024 artfynd.xlsx
+++ b/artfynd/A 33954-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122747228</v>
       </c>
       <c r="B4" t="n">
-        <v>93198</v>
+        <v>93200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33954-2024 artfynd.xlsx
+++ b/artfynd/A 33954-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122747228</v>
       </c>
       <c r="B4" t="n">
-        <v>93200</v>
+        <v>93201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33954-2024 artfynd.xlsx
+++ b/artfynd/A 33954-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122747228</v>
       </c>
       <c r="B4" t="n">
-        <v>93201</v>
+        <v>93204</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33954-2024 artfynd.xlsx
+++ b/artfynd/A 33954-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122747228</v>
       </c>
       <c r="B4" t="n">
-        <v>93204</v>
+        <v>93205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
